--- a/data/trans_bre/P1401-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1401-Edad-trans_bre.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-52,0%</t>
+          <t>-49,0%</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,13</t>
+          <t>-1,27; -0,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,36</t>
+          <t>-1,51; 0,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>103,1%</t>
         </is>
       </c>
     </row>
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,08</t>
+          <t>-0,41; 2,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,48</t>
+          <t>0,41; 2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,3</t>
+          <t>-0,38; 1,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 602,87</t>
+          <t>-52,65; 710,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,48; —</t>
+          <t>-67,5; —</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>137,78%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,36</t>
+          <t>0,74; 4,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,7</t>
+          <t>-0,15; 2,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,8</t>
+          <t>-0,16; 2,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,0; 1191,67</t>
+          <t>31,78; 1200,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 623,35</t>
+          <t>-28,88; 519,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 651,87</t>
+          <t>-11,99; 336,84</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,37%</t>
+          <t>-2,23%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,31</t>
+          <t>0,57; 5,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,5</t>
+          <t>0,12; 3,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,43</t>
+          <t>-1,91; 1,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 548,8</t>
+          <t>8,47; 568,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 784,54</t>
+          <t>-8,8; 745,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 56,98</t>
+          <t>-44,37; 72,22</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-29,03%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,51</t>
+          <t>-3,42; 2,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,93</t>
+          <t>0,61; 5,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,03</t>
+          <t>-2,0; 2,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 138,9</t>
+          <t>-64,17; 164,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,7; 748,11</t>
+          <t>7,95; 712,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,41; 29,78</t>
+          <t>-34,88; 80,36</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-2,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-39,52%</t>
+          <t>-42,12%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,13</t>
+          <t>-3,07; 2,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,24</t>
+          <t>-3,92; 2,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -0,14</t>
+          <t>-6,01; -0,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 154,53</t>
+          <t>-68,7; 154,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 80,14</t>
+          <t>-64,75; 104,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -2,11</t>
+          <t>-64,38; -4,01</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,56</t>
+          <t>0,31; 1,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,81</t>
+          <t>0,51; 1,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,79</t>
+          <t>-0,44; 0,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,58; 170,25</t>
+          <t>19,84; 166,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,74; 254,37</t>
+          <t>47,99; 249,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 48,63</t>
+          <t>-18,13; 41,71</t>
         </is>
       </c>
     </row>
